--- a/data/trans_dic/P64D1_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P64D1_R-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>31,66%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,81; 24,07</t>
+          <t>15,53; 32,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>42,43; 65,39</t>
+          <t>38,42; 56,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23,82; 37,4</t>
+          <t>25,77; 38,48</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>30,08%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,03; 23,93</t>
+          <t>21,19; 26,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>34,28; 54,66</t>
+          <t>35,46; 40,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20,14; 34,43</t>
+          <t>28,06; 32,19</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>31,09%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22,98; 32,31</t>
+          <t>23,58; 31,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30,72; 38,4</t>
+          <t>31,21; 38,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28,02; 33,82</t>
+          <t>28,37; 34,31</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>30,48%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,53; 24,28</t>
+          <t>22,66; 27,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>35,44; 48,72</t>
+          <t>35,57; 40,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23,07; 33,2</t>
+          <t>28,96; 32,09</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>20913</t>
+          <t>37812</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>42450</t>
+          <t>41945</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>63363</t>
+          <t>79757</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12954; 31803</t>
+          <t>25462; 53515</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>34136; 52604</t>
+          <t>33811; 50096</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>50623; 79498</t>
+          <t>64917; 96946</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>263069</t>
+          <t>303712</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>385312</t>
+          <t>362855</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>648381</t>
+          <t>666567</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>138611; 330864</t>
+          <t>269283; 340639</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>323974; 516549</t>
+          <t>335155; 386987</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>468646; 801297</t>
+          <t>621828; 713333</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>122748</t>
+          <t>134296</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>148495</t>
+          <t>165766</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>271243</t>
+          <t>300063</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>102796; 144515</t>
+          <t>114950; 155742</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>133745; 167193</t>
+          <t>149037; 185008</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>247356; 298503</t>
+          <t>273777; 331088</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>406730</t>
+          <t>475820</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>576256</t>
+          <t>570567</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>982987</t>
+          <t>1046387</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>265480; 476367</t>
+          <t>435580; 523814</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>517723; 711668</t>
+          <t>537425; 604874</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>789432; 1136263</t>
+          <t>993988; 1101438</t>
         </is>
       </c>
     </row>
